--- a/data/trans_orig/IP24_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Edad-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según el ejercicio físico  que realiza en su tiempo libre / solo 2023 en 2023 (tasa de respuesta: 99,43%)</t>
+          <t>Menores según el ejercicio físico que realiza en su tiempo libre / solo 2023 en 2023 (tasa de respuesta: 99,43%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>3320</t>
+          <t>3103</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10436</t>
+          <t>10140</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,64%</t>
+          <t>18,11%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2178</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8362</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,57%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>13,81%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6662</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>15606</t>
+          <t>16260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>13,62%</t>
+          <t>14,19%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1161</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7349</t>
+          <t>7181</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>12,82%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>442</t>
+          <t>444</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>4489</t>
+          <t>5125</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2074</t>
+          <t>2143</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>9080</t>
+          <t>8882</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,87%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>7,75%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>855</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6138</t>
+          <t>6274</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -996,7 +996,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5354</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>9,14%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1724</t>
+          <t>1606</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8566</t>
+          <t>8295</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,5%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,48%</t>
+          <t>7,24%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>13640</t>
+          <t>13507</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23902</t>
+          <t>24312</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,12%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>42,68%</t>
+          <t>43,41%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>14601</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26499</t>
+          <t>25909</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>45,24%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31151</t>
+          <t>31762</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46797</t>
+          <t>46976</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>41,0%</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>11759</t>
+          <t>12021</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>21306</t>
+          <t>22327</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1197,12 +1197,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,47%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>38,05%</t>
+          <t>39,87%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1217,12 +1217,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16008</t>
+          <t>16433</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27423</t>
+          <t>27233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1232,12 +1232,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,5%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1252,12 +1252,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>31351</t>
+          <t>30716</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46336</t>
+          <t>46142</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>26,81%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,44%</t>
+          <t>40,27%</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>5110</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>12740</t>
+          <t>12671</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1310,12 +1310,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,13%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22,75%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1330,12 +1330,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>6092</t>
+          <t>5803</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13387</t>
+          <t>13491</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1345,12 +1345,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>10,4%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>22,86%</t>
+          <t>23,03%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>13005</t>
+          <t>12899</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24602</t>
+          <t>24091</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1380,12 +1380,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,26%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,03%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2095</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>8428</t>
+          <t>8038</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3216</t>
+          <t>3694</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12406</t>
+          <t>12628</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>2,03%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6749</t>
+          <t>6841</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17429</t>
+          <t>17582</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,15%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4861</t>
+          <t>4892</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>13129</t>
+          <t>13012</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7313</t>
+          <t>7534</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18226</t>
+          <t>19216</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>4,14%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,55%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>14278</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>29562</t>
+          <t>28641</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,39%</t>
         </is>
       </c>
     </row>
@@ -1751,12 +1751,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14392</t>
+          <t>14261</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>27792</t>
+          <t>27655</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>17,45%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1786,12 +1786,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31967</t>
+          <t>31887</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52561</t>
+          <t>52471</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1801,12 +1801,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,56%</t>
+          <t>17,51%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>28,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1821,12 +1821,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>49576</t>
+          <t>50226</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74280</t>
+          <t>74083</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1836,12 +1836,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,76%</t>
+          <t>21,7%</t>
         </is>
       </c>
     </row>
@@ -1864,12 +1864,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>81752</t>
+          <t>81147</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102975</t>
+          <t>101940</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1879,12 +1879,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,32%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>64,64%</t>
+          <t>63,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1899,12 +1899,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>80184</t>
+          <t>81218</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104309</t>
+          <t>104041</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1914,12 +1914,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,04%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,28%</t>
+          <t>57,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1934,12 +1934,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>169807</t>
+          <t>170225</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>201089</t>
+          <t>201278</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1949,12 +1949,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,74%</t>
+          <t>49,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,9%</t>
+          <t>58,96%</t>
         </is>
       </c>
     </row>
@@ -1977,12 +1977,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19032</t>
+          <t>18982</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>38003</t>
+          <t>38368</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1992,12 +1992,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11,95%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>24,09%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2012,12 +2012,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14143</t>
+          <t>14682</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28134</t>
+          <t>29186</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2027,12 +2027,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>16,03%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2047,12 +2047,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>37376</t>
+          <t>37435</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>61198</t>
+          <t>60014</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,95%</t>
+          <t>10,97%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,58%</t>
         </is>
       </c>
     </row>
@@ -2090,12 +2090,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3293</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11076</t>
+          <t>10909</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2110,7 +2110,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2125,12 +2125,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4579</t>
+          <t>4661</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13861</t>
+          <t>14123</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2160,12 +2160,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9382</t>
+          <t>9537</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21184</t>
+          <t>21460</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,29%</t>
         </is>
       </c>
     </row>
@@ -2320,12 +2320,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>714</t>
+          <t>727</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>6127</t>
+          <t>6863</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2335,12 +2335,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2360,7 +2360,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>5466</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2390,12 +2390,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1021</t>
+          <t>1389</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8735</t>
+          <t>8207</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2405,12 +2405,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,36%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -2433,12 +2433,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11986</t>
+          <t>12509</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>31388</t>
+          <t>30441</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2448,12 +2448,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>17,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2468,12 +2468,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21514</t>
+          <t>21554</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>41125</t>
+          <t>42014</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,19%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,44%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2503,12 +2503,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>37609</t>
+          <t>36886</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63531</t>
+          <t>61232</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,59%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>15,92%</t>
         </is>
       </c>
     </row>
@@ -2546,12 +2546,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28983</t>
+          <t>28223</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>47409</t>
+          <t>47092</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2561,12 +2561,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>27,39%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2581,12 +2581,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>44727</t>
+          <t>45359</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71336</t>
+          <t>71111</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2616,12 +2616,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>80682</t>
+          <t>78359</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111928</t>
+          <t>111284</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -2659,12 +2659,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>81136</t>
+          <t>82076</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>105485</t>
+          <t>106422</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2674,12 +2674,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>60,95%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80337</t>
+          <t>80443</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>108085</t>
+          <t>109943</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2709,12 +2709,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>37,98%</t>
+          <t>38,02%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,09%</t>
+          <t>51,97%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>169144</t>
+          <t>170045</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>206122</t>
+          <t>207049</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2744,12 +2744,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>44,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>53,83%</t>
         </is>
       </c>
     </row>
@@ -2772,12 +2772,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>11852</t>
+          <t>11868</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>26137</t>
+          <t>26028</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2787,12 +2787,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>6,85%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16714</t>
+          <t>16186</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34684</t>
+          <t>34583</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2822,12 +2822,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,9%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,39%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32232</t>
+          <t>32205</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>53847</t>
+          <t>55918</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2857,12 +2857,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,38%</t>
+          <t>8,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,54%</t>
         </is>
       </c>
     </row>
@@ -2885,12 +2885,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>814</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>7113</t>
+          <t>6882</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2905,7 +2905,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2920,12 +2920,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1464</t>
+          <t>1236</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9534</t>
+          <t>9480</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2935,12 +2935,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2955,12 +2955,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3207</t>
+          <t>3041</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>13214</t>
+          <t>12481</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2970,12 +2970,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -3115,12 +3115,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>649</t>
+          <t>453</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>6064</t>
+          <t>6519</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3130,12 +3130,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2979</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1028</t>
+          <t>1076</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6644</t>
+          <t>6755</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3200,12 +3200,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,16%</t>
         </is>
       </c>
     </row>
@@ -3228,12 +3228,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>17407</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>34968</t>
+          <t>36242</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3243,12 +3243,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3263,12 +3263,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40115</t>
+          <t>40332</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>67005</t>
+          <t>66242</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3278,12 +3278,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>13,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,93%</t>
+          <t>21,68%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3298,12 +3298,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>63239</t>
+          <t>63088</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>96592</t>
+          <t>96759</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>10,86%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -3341,12 +3341,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>45544</t>
+          <t>44958</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>80321</t>
+          <t>79986</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3356,12 +3356,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>16,53%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>29,04%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3376,12 +3376,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>66504</t>
+          <t>68060</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>103079</t>
+          <t>104768</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>22,28%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>34,3%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3411,12 +3411,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>120761</t>
+          <t>120347</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>173594</t>
+          <t>172134</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3426,12 +3426,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,79%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,88%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -3454,12 +3454,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>74344</t>
+          <t>77093</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>124537</t>
+          <t>125790</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3469,12 +3469,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,99%</t>
+          <t>27,99%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>45,21%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3489,12 +3489,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>97988</t>
+          <t>101042</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>137857</t>
+          <t>139455</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3504,12 +3504,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>32,08%</t>
+          <t>33,08%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3524,12 +3524,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>190081</t>
+          <t>187545</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>253952</t>
+          <t>253515</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3539,12 +3539,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,28%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,64%</t>
         </is>
       </c>
     </row>
@@ -3567,12 +3567,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>41503</t>
+          <t>40555</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>128545</t>
+          <t>130083</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3582,12 +3582,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,07%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>46,67%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3602,12 +3602,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27208</t>
+          <t>27339</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>80377</t>
+          <t>75007</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3617,12 +3617,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>26,31%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3637,12 +3637,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>75966</t>
+          <t>77211</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>200496</t>
+          <t>194129</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3652,12 +3652,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>33,42%</t>
         </is>
       </c>
     </row>
@@ -3680,47 +3680,47 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>2930</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>13468</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>2,4%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>1,06%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>4,89%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>6494</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>2708</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>12863</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>2,4%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>4,67%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="K30" s="2" t="inlineStr">
-        <is>
-          <t>6494</t>
-        </is>
-      </c>
-      <c r="L30" s="2" t="inlineStr">
-        <is>
-          <t>2878</t>
-        </is>
-      </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>14069</t>
+          <t>13878</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3730,12 +3730,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3750,12 +3750,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>7458</t>
+          <t>6975</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>21954</t>
+          <t>21424</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,28%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -3910,12 +3910,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>9154</t>
+          <t>9932</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>21819</t>
+          <t>21777</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3925,12 +3925,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3945,12 +3945,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8989</t>
+          <t>8179</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>20840</t>
+          <t>19949</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3960,12 +3960,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3980,12 +3980,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>20348</t>
+          <t>21064</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>36834</t>
+          <t>37083</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3995,12 +3995,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4023,12 +4023,12 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>43971</t>
+          <t>44882</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>70590</t>
+          <t>72726</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4038,12 +4038,12 @@
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
@@ -4058,12 +4058,12 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>79863</t>
+          <t>81121</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>118002</t>
+          <t>114773</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4073,12 +4073,12 @@
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,15%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4093,12 +4093,12 @@
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>131899</t>
+          <t>131762</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>175413</t>
+          <t>174382</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4108,12 +4108,12 @@
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -4136,12 +4136,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>103671</t>
+          <t>105673</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>143876</t>
+          <t>145262</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4151,47 +4151,47 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>15,62%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
+          <t>21,88%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="K34" s="2" t="inlineStr">
+        <is>
+          <t>184903</t>
+        </is>
+      </c>
+      <c r="L34" s="2" t="inlineStr">
+        <is>
+          <t>164197</t>
+        </is>
+      </c>
+      <c r="M34" s="2" t="inlineStr">
+        <is>
+          <t>211456</t>
+        </is>
+      </c>
+      <c r="N34" s="2" t="inlineStr">
+        <is>
+          <t>24,4%</t>
+        </is>
+      </c>
+      <c r="O34" s="2" t="inlineStr">
+        <is>
           <t>21,67%</t>
         </is>
       </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
-      <c r="K34" s="2" t="inlineStr">
-        <is>
-          <t>184903</t>
-        </is>
-      </c>
-      <c r="L34" s="2" t="inlineStr">
-        <is>
-          <t>160068</t>
-        </is>
-      </c>
-      <c r="M34" s="2" t="inlineStr">
-        <is>
-          <t>208894</t>
-        </is>
-      </c>
-      <c r="N34" s="2" t="inlineStr">
-        <is>
-          <t>24,4%</t>
-        </is>
-      </c>
-      <c r="O34" s="2" t="inlineStr">
-        <is>
-          <t>21,13%</t>
-        </is>
-      </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,91%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4206,12 +4206,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>277958</t>
+          <t>277124</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>340459</t>
+          <t>340671</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,55%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,97%</t>
         </is>
       </c>
     </row>
@@ -4249,12 +4249,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>267540</t>
+          <t>268662</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>338461</t>
+          <t>339342</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4264,12 +4264,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>40,3%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4284,12 +4284,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>300602</t>
+          <t>300735</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>354319</t>
+          <t>354232</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>39,67%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>46,76%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4319,12 +4319,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>592783</t>
+          <t>589720</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>677064</t>
+          <t>678934</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4334,12 +4334,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,49%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>47,63%</t>
+          <t>47,76%</t>
         </is>
       </c>
     </row>
@@ -4362,12 +4362,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>100260</t>
+          <t>100131</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>214550</t>
+          <t>210399</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4377,12 +4377,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>32,32%</t>
+          <t>31,69%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4397,12 +4397,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>90871</t>
+          <t>89522</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>142995</t>
+          <t>140398</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>201674</t>
+          <t>200740</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>324572</t>
+          <t>316091</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,24%</t>
         </is>
       </c>
     </row>
@@ -4475,12 +4475,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>17615</t>
+          <t>18261</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>33793</t>
+          <t>33730</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4490,12 +4490,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4510,12 +4510,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>19440</t>
+          <t>20456</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>37067</t>
+          <t>37459</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,94%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>41705</t>
+          <t>42766</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>66370</t>
+          <t>66569</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP24_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Edad-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>3817</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>1737</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>6839</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>7,91%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>3,6%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>14,17%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>11</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>5949</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>3103</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>10140</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>10,62%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>5,54%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>18,11%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>4618</t>
+          <t>5729</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2178</t>
+          <t>2921</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8091</t>
+          <t>9972</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>7,88%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>19,64%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>10567</t>
+          <t>9547</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6005</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>16260</t>
+          <t>14323</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>14,19%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>1565</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>487</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>4337</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>8,99%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>3211</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>1265</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>7181</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>5,73%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>2,26%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>12,82%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>3251</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>444</t>
+          <t>1286</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>5125</t>
+          <t>7109</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>8,75%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>4965</t>
+          <t>4816</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2143</t>
+          <t>2213</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8882</t>
+          <t>9331</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>9,42%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>3575</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>1,89%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>7,41%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>2744</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>855</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>6274</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>4,9%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,53%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>11,2%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1252</t>
+          <t>2446</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>754</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5354</t>
+          <t>5214</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>4,82%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>10,27%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3996</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1606</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8295</t>
+          <t>7232</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,39%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,3%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>16708</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>12292</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>21986</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>34,62%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>25,47%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>45,56%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>34</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>18744</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>13507</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>24312</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>33,47%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>24,12%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>43,41%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>35</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>20268</t>
+          <t>17952</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>14601</t>
+          <t>13258</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>25909</t>
+          <t>23180</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>34,6%</t>
+          <t>35,35%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>26,11%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>39012</t>
+          <t>34660</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31762</t>
+          <t>28167</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>46976</t>
+          <t>41336</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>35,0%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,72%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,74%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>18147</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>13804</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>23058</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>37,61%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>28,61%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>47,78%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>16782</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>12021</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>22327</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>29,97%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>21,47%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>39,87%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>21482</t>
+          <t>14536</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>16433</t>
+          <t>10301</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>27233</t>
+          <t>19287</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>20,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>46,5%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>38263</t>
+          <t>32684</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>30716</t>
+          <t>26820</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>46142</t>
+          <t>40085</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>33,4%</t>
+          <t>33,0%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>26,81%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>40,47%</t>
         </is>
       </c>
     </row>
@@ -1285,72 +1285,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>7110</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>4598</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>10720</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>14,73%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>9,53%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>22,21%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>18</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>8571</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>5110</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>12671</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>15,3%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>9,13%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>22,63%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>9198</t>
+          <t>6864</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>5803</t>
+          <t>4298</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>13491</t>
+          <t>10454</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>8,46%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>23,03%</t>
+          <t>20,59%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1360,32 +1360,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>17768</t>
+          <t>13974</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>10108</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>24091</t>
+          <t>19320</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>15,51%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>11,26%</t>
+          <t>10,21%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>19,51%</t>
         </is>
       </c>
     </row>
@@ -1398,74 +1398,74 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>48257</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>48257</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>48257</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>106</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>56000</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>56000</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>56000</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>50779</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>50779</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>50779</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>58571</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>58571</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>58571</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>216</t>
@@ -1473,17 +1473,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>114571</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>114571</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>114571</t>
+          <t>99036</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>5269</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2789</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>9202</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>3,35%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,77%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>5,86%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>4349</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2095</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>8038</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2,73%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,32%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>6884</t>
+          <t>4130</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3694</t>
+          <t>1938</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>12628</t>
+          <t>7909</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>6,94%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,22 +1590,22 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>11233</t>
+          <t>9398</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>6841</t>
+          <t>6060</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>17582</t>
+          <t>15003</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -1628,72 +1628,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10513</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>6356</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16082</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>6,69%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>4,04%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>10,23%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>8168</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>4892</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>13012</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>3,07%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>12131</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>7534</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19216</t>
+          <t>13257</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>3,35%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>20299</t>
+          <t>18711</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14278</t>
+          <t>13094</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>28641</t>
+          <t>26154</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,64%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>36237</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>28005</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>45876</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>23,06%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>17,82%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>29,19%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>20296</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>14261</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>27655</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>12,74%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>8,95%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>17,36%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>57</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41505</t>
+          <t>19643</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>31887</t>
+          <t>13882</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>52471</t>
+          <t>26796</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>13,5%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,51%</t>
+          <t>9,54%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>28,82%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>61802</t>
+          <t>55881</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>50226</t>
+          <t>45067</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>74083</t>
+          <t>67279</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>22,23%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>81477</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>71089</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>91411</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>51,84%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>45,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>58,16%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>92841</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>81147</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>101940</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>58,28%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>50,94%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>63,99%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>142</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>92659</t>
+          <t>87570</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>81218</t>
+          <t>78725</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>104041</t>
+          <t>96278</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>60,18%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>44,6%</t>
+          <t>54,1%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>66,16%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>185500</t>
+          <t>169047</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>170225</t>
+          <t>153550</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>201278</t>
+          <t>182613</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>54,34%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,73%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,96%</t>
+          <t>60,33%</t>
         </is>
       </c>
     </row>
@@ -1967,72 +1967,72 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>17187</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>12091</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>24362</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>10,94%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>7,69%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>15,5%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>37</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>27146</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>18982</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>38368</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>17,04%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>11,92%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>24,09%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>20948</t>
+          <t>20081</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>14682</t>
+          <t>14401</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>29186</t>
+          <t>26424</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,06%</t>
+          <t>9,9%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2042,32 +2042,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>48093</t>
+          <t>37269</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>37435</t>
+          <t>29202</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>60014</t>
+          <t>46940</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>14,09%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>9,65%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>17,58%</t>
+          <t>15,51%</t>
         </is>
       </c>
     </row>
@@ -2080,72 +2080,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>6479</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>3382</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>11232</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>4,12%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>7,15%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>6498</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>3293</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>10909</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>4,08%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2,07%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>6,85%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>7964</t>
+          <t>5896</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>4661</t>
+          <t>3153</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14123</t>
+          <t>11078</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,05%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2155,32 +2155,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>14462</t>
+          <t>12376</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9537</t>
+          <t>7993</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21460</t>
+          <t>18953</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,09%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,26%</t>
         </is>
       </c>
     </row>
@@ -2193,74 +2193,74 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>157163</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>157163</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>157163</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>159299</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>145518</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>145518</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>145518</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="O17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="P17" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>275</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>182090</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>182090</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>182090</t>
-        </is>
-      </c>
-      <c r="N17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P17" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q17" s="2" t="inlineStr">
         <is>
           <t>533</t>
@@ -2268,17 +2268,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>341389</t>
+          <t>302681</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>341389</t>
+          <t>302681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>341389</t>
+          <t>302681</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>1254</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>5417</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>2,72%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>2379</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>727</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>6863</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>1,37%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>3,97%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>1027</t>
+          <t>2568</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>819</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5466</t>
+          <t>7792</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>3405</t>
+          <t>3822</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1389</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>8207</t>
+          <t>8666</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>28452</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>20158</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>37921</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>14,29%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>10,12%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>19,04%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>25</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>18422</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>12509</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>30441</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>10,64%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>7,23%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>17,59%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>29941</t>
+          <t>16631</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>21554</t>
+          <t>11040</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>42014</t>
+          <t>25074</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>48363</t>
+          <t>45083</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>36886</t>
+          <t>33696</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>61232</t>
+          <t>55919</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>12,57%</t>
+          <t>12,06%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>9,59%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>14,96%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>53819</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>42781</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>66195</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>27,02%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>21,48%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>33,24%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>52</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>37505</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>28223</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>47092</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>21,67%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>16,31%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>27,21%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>57728</t>
+          <t>39134</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>45359</t>
+          <t>29679</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>71111</t>
+          <t>49905</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>27,29%</t>
+          <t>22,4%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>21,44%</t>
+          <t>16,99%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>33,61%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>95233</t>
+          <t>92953</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>78359</t>
+          <t>78506</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>111284</t>
+          <t>108304</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>24,76%</t>
+          <t>24,86%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -2649,72 +2649,72 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>91218</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>79250</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>105802</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>45,8%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>39,79%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>53,12%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>126</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>93882</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>82076</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>106422</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr">
-        <is>
-          <t>54,24%</t>
-        </is>
-      </c>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>47,42%</t>
-        </is>
-      </c>
-      <c r="I21" s="2" t="inlineStr">
-        <is>
-          <t>61,49%</t>
-        </is>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>110</t>
-        </is>
-      </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>94407</t>
+          <t>94884</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>80443</t>
+          <t>83097</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>109943</t>
+          <t>105646</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>54,32%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>38,02%</t>
+          <t>47,57%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>51,97%</t>
+          <t>60,48%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2724,32 +2724,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>188290</t>
+          <t>186102</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>170045</t>
+          <t>166913</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>207049</t>
+          <t>202652</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>44,21%</t>
+          <t>44,65%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>53,83%</t>
+          <t>54,21%</t>
         </is>
       </c>
     </row>
@@ -2762,72 +2762,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>20482</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>13363</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>29608</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>10,28%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>6,71%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>14,87%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>23</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>18069</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>11868</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>26028</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>10,44%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>6,86%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>15,04%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>24279</t>
+          <t>18174</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>16186</t>
+          <t>12318</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34583</t>
+          <t>27257</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>7,65%</t>
+          <t>7,05%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2837,32 +2837,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>42348</t>
+          <t>38656</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>32205</t>
+          <t>29641</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>55918</t>
+          <t>51222</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>8,37%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,54%</t>
+          <t>13,7%</t>
         </is>
       </c>
     </row>
@@ -2875,72 +2875,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>3938</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>1327</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>9888</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>1,98%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>0,67%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>4,96%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>2815</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>814</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>6882</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>1,63%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0,47%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>3,98%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4170</t>
+          <t>3280</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1236</t>
+          <t>878</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>9480</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2950,32 +2950,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>6985</t>
+          <t>7218</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>3041</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>12481</t>
+          <t>14054</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -2988,74 +2988,74 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>199163</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>199163</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>199163</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>233</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>173072</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>174672</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>174672</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>174672</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H24" s="2" t="inlineStr">
+      <c r="O24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I24" s="2" t="inlineStr">
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>242</t>
-        </is>
-      </c>
-      <c r="K24" s="2" t="inlineStr">
-        <is>
-          <t>211553</t>
-        </is>
-      </c>
-      <c r="L24" s="2" t="inlineStr">
-        <is>
-          <t>211553</t>
-        </is>
-      </c>
-      <c r="M24" s="2" t="inlineStr">
-        <is>
-          <t>211553</t>
-        </is>
-      </c>
-      <c r="N24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P24" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q24" s="2" t="inlineStr">
         <is>
           <t>475</t>
@@ -3063,17 +3063,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>384625</t>
+          <t>373835</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>384625</t>
+          <t>373835</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>384625</t>
+          <t>373835</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3105,72 +3105,72 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>727</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3052</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>1,04%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>2178</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>453</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>6519</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr">
-        <is>
-          <t>0,79%</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="inlineStr">
-        <is>
-          <t>2,37%</t>
-        </is>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>842</t>
+          <t>2306</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>744</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>6931</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,22 +3180,22 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>3021</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1076</t>
+          <t>1059</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6755</t>
+          <t>7337</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
@@ -3205,7 +3205,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,34%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>53790</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>41947</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>67787</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>18,38%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>14,33%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>23,16%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>41</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>26046</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>17315</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>36242</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>9,46%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>6,29%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>13,16%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>52963</t>
+          <t>26928</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>40332</t>
+          <t>19219</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>66242</t>
+          <t>36094</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>14,07%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>79009</t>
+          <t>80718</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>63088</t>
+          <t>66614</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>96759</t>
+          <t>98756</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>13,6%</t>
+          <t>14,7%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>10,86%</t>
+          <t>12,13%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,66%</t>
+          <t>17,98%</t>
         </is>
       </c>
     </row>
@@ -3331,72 +3331,72 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>83799</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>68250</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>102911</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>28,64%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>23,32%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>35,17%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>91</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>64880</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>44958</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>79986</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>23,55%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>16,32%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>29,04%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>84417</t>
+          <t>70115</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>68060</t>
+          <t>56437</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>104768</t>
+          <t>82992</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,0%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3406,32 +3406,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>149296</t>
+          <t>153914</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>120347</t>
+          <t>132079</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>172134</t>
+          <t>176976</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>25,7%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>29,63%</t>
+          <t>32,22%</t>
         </is>
       </c>
     </row>
@@ -3444,72 +3444,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>112329</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>95256</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>130816</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>38,38%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>32,55%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>44,7%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>148</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>106839</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>77093</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>125790</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>38,79%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>27,99%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>45,67%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>119800</t>
+          <t>113949</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>101042</t>
+          <t>100161</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>139455</t>
+          <t>128491</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>44,42%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>39,04%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>45,65%</t>
+          <t>50,08%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3519,32 +3519,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>226639</t>
+          <t>226278</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>187545</t>
+          <t>201886</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>253515</t>
+          <t>247294</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>39,01%</t>
+          <t>41,2%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>32,28%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>43,64%</t>
+          <t>45,03%</t>
         </is>
       </c>
     </row>
@@ -3557,72 +3557,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>35476</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>24265</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>61787</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>12,12%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>8,29%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>21,11%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>51</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>68911</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>40555</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>130083</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>25,02%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>14,72%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>47,22%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>36</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>40967</t>
+          <t>36356</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>27339</t>
+          <t>26657</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>75007</t>
+          <t>47091</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>13,41%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>18,36%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3632,32 +3632,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>109878</t>
+          <t>71832</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>77211</t>
+          <t>56687</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>194129</t>
+          <t>100838</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>10,32%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>18,36%</t>
         </is>
       </c>
     </row>
@@ -3675,32 +3675,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>6604</t>
+          <t>6524</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2883</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>13468</t>
+          <t>13502</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3710,32 +3710,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>6494</t>
+          <t>6899</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2708</t>
+          <t>3414</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>13878</t>
+          <t>13206</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3745,32 +3745,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>13098</t>
+          <t>13423</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6975</t>
+          <t>7757</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>21424</t>
+          <t>20996</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -3788,17 +3788,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>275458</t>
+          <t>292645</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>305483</t>
+          <t>256553</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3858,17 +3858,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>580940</t>
+          <t>549198</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3900,107 +3900,107 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>11067</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>7053</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>17625</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>1,59%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>2,53%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>14855</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>9932</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>21777</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>2,24%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>1,5%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>13370</t>
+          <t>14734</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>8179</t>
+          <t>9328</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>19949</t>
+          <t>21125</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="Q32" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="R32" s="2" t="inlineStr">
+        <is>
+          <t>25801</t>
+        </is>
+      </c>
+      <c r="S32" s="2" t="inlineStr">
+        <is>
+          <t>18889</t>
+        </is>
+      </c>
+      <c r="T32" s="2" t="inlineStr">
+        <is>
+          <t>34831</t>
+        </is>
+      </c>
+      <c r="U32" s="2" t="inlineStr">
+        <is>
+          <t>1,95%</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>1,43%</t>
+        </is>
+      </c>
+      <c r="W32" s="2" t="inlineStr">
+        <is>
           <t>2,63%</t>
-        </is>
-      </c>
-      <c r="Q32" s="2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="R32" s="2" t="inlineStr">
-        <is>
-          <t>28225</t>
-        </is>
-      </c>
-      <c r="S32" s="2" t="inlineStr">
-        <is>
-          <t>21064</t>
-        </is>
-      </c>
-      <c r="T32" s="2" t="inlineStr">
-        <is>
-          <t>37083</t>
-        </is>
-      </c>
-      <c r="U32" s="2" t="inlineStr">
-        <is>
-          <t>1,99%</t>
-        </is>
-      </c>
-      <c r="V32" s="2" t="inlineStr">
-        <is>
-          <t>1,48%</t>
-        </is>
-      </c>
-      <c r="W32" s="2" t="inlineStr">
-        <is>
-          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -4013,72 +4013,72 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>94319</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>79290</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>113187</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>13,53%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>11,37%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>16,23%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>55847</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>44882</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>72726</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>8,41%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>6,76%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>10,96%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>124</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>96789</t>
+          <t>55008</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>81121</t>
+          <t>44740</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>114773</t>
+          <t>67125</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
         <is>
-          <t>12,77%</t>
+          <t>8,77%</t>
         </is>
       </c>
       <c r="O33" s="2" t="inlineStr">
         <is>
-          <t>10,71%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="P33" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="Q33" s="2" t="inlineStr">
@@ -4088,32 +4088,32 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>152636</t>
+          <t>149328</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>131762</t>
+          <t>129735</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>174382</t>
+          <t>170692</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
         <is>
-          <t>10,74%</t>
+          <t>11,27%</t>
         </is>
       </c>
       <c r="V33" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="W33" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -4126,72 +4126,72 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>174766</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>152743</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>199469</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>25,07%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>21,91%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>28,61%</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
           <t>183</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>125424</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>105673</t>
-        </is>
-      </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>145262</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>18,89%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>15,92%</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="inlineStr">
-        <is>
-          <t>21,88%</t>
-        </is>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>218</t>
-        </is>
-      </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>184903</t>
+          <t>131338</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>164197</t>
+          <t>114351</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>211456</t>
+          <t>152141</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>18,22%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4201,32 +4201,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>310327</t>
+          <t>306104</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>277124</t>
+          <t>277603</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>340671</t>
+          <t>337157</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>21,83%</t>
+          <t>23,11%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,96%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>23,97%</t>
+          <t>25,45%</t>
         </is>
       </c>
     </row>
@@ -4239,72 +4239,72 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>417</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>301731</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>277875</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>327411</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>43,28%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>39,85%</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>46,96%</t>
+        </is>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
           <t>456</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>312307</t>
-        </is>
-      </c>
-      <c r="E35" s="2" t="inlineStr">
-        <is>
-          <t>268662</t>
-        </is>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>339342</t>
-        </is>
-      </c>
-      <c r="G35" s="2" t="inlineStr">
-        <is>
-          <t>47,05%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>40,47%</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="inlineStr">
-        <is>
-          <t>51,12%</t>
-        </is>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>417</t>
-        </is>
-      </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>327134</t>
+          <t>314355</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>300735</t>
+          <t>293352</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>354232</t>
+          <t>336033</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>43,17%</t>
+          <t>50,09%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>39,69%</t>
+          <t>46,75%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>46,75%</t>
+          <t>53,55%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4314,32 +4314,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>639441</t>
+          <t>616087</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>589720</t>
+          <t>582175</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>678934</t>
+          <t>648423</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>46,51%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>41,49%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>47,76%</t>
+          <t>48,95%</t>
         </is>
       </c>
     </row>
@@ -4352,57 +4352,57 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>91293</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>76625</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>120786</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>13,09%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>10,99%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>17,32%</t>
+        </is>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
           <t>143</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>130908</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>100131</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>210399</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr">
-        <is>
-          <t>19,72%</t>
-        </is>
-      </c>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>15,08%</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="inlineStr">
-        <is>
-          <t>31,69%</t>
-        </is>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>139</t>
-        </is>
-      </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>107675</t>
+          <t>89148</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>89522</t>
+          <t>75151</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>140398</t>
+          <t>104111</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4427,32 +4427,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>238583</t>
+          <t>180441</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>200740</t>
+          <t>159353</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>316091</t>
+          <t>211488</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>16,78%</t>
+          <t>13,62%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>14,12%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>15,96%</t>
         </is>
       </c>
     </row>
@@ -4465,72 +4465,72 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>24051</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>17939</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>33343</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>3,45%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>2,57%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>4,78%</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>24488</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>18261</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>33730</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>2,75%</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>5,08%</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>27826</t>
+          <t>22939</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>20456</t>
+          <t>16452</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>37459</t>
+          <t>32380</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>5,16%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4540,32 +4540,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>52314</t>
+          <t>46990</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>42766</t>
+          <t>38154</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>66569</t>
+          <t>59362</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,48%</t>
         </is>
       </c>
     </row>
@@ -4578,74 +4578,74 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>969</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>697228</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
           <t>939</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>663829</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr">
+      <c r="K38" s="2" t="inlineStr">
+        <is>
+          <t>627522</t>
+        </is>
+      </c>
+      <c r="L38" s="2" t="inlineStr">
+        <is>
+          <t>627522</t>
+        </is>
+      </c>
+      <c r="M38" s="2" t="inlineStr">
+        <is>
+          <t>627522</t>
+        </is>
+      </c>
+      <c r="N38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="O38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="I38" s="2" t="inlineStr">
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>969</t>
-        </is>
-      </c>
-      <c r="K38" s="2" t="inlineStr">
-        <is>
-          <t>757697</t>
-        </is>
-      </c>
-      <c r="L38" s="2" t="inlineStr">
-        <is>
-          <t>757697</t>
-        </is>
-      </c>
-      <c r="M38" s="2" t="inlineStr">
-        <is>
-          <t>757697</t>
-        </is>
-      </c>
-      <c r="N38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="O38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="P38" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
       <c r="Q38" s="2" t="inlineStr">
         <is>
           <t>1908</t>
@@ -4653,17 +4653,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>1421526</t>
+          <t>1324750</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">

--- a/data/trans_orig/IP24_2023-Edad-trans_orig.xlsx
+++ b/data/trans_orig/IP24_2023-Edad-trans_orig.xlsx
@@ -1007,7 +1007,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C8" s="5" t="n">
@@ -1508,7 +1508,7 @@
       <c r="A15" s="1" t="n"/>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C15" s="5" t="n">
@@ -2009,7 +2009,7 @@
       <c r="A22" s="1" t="n"/>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C22" s="5" t="n">
@@ -2510,7 +2510,7 @@
       <c r="A29" s="1" t="n"/>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C29" s="5" t="n">
@@ -3011,7 +3011,7 @@
       <c r="A36" s="1" t="n"/>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>No hace ejercicio,. Su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
+          <t>No hace ejercicio, su tiempo libre lo ocupa de forma casi completamente sedentaria (leer, ver la televisión, ir al cine</t>
         </is>
       </c>
       <c r="C36" s="5" t="n">
